--- a/figuras/proporcoes_e_IC_ativos_fisicamente_desloc.xlsx
+++ b/figuras/proporcoes_e_IC_ativos_fisicamente_desloc.xlsx
@@ -391,13 +391,13 @@
         <v>2009</v>
       </c>
       <c r="B2">
-        <v>0.1880776493819341</v>
+        <v>0.1793754328520114</v>
       </c>
       <c r="C2">
-        <v>0.1809163037834675</v>
+        <v>0.1723315638807554</v>
       </c>
       <c r="D2">
-        <v>0.1954548238278458</v>
+        <v>0.1866422875477348</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -406,7 +406,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.188 (0.181; 0.195)</t>
+          <t>0.179 (0.172; 0.187)</t>
         </is>
       </c>
     </row>
@@ -415,13 +415,13 @@
         <v>2010</v>
       </c>
       <c r="B3">
-        <v>0.1946017877268642</v>
+        <v>0.1883331456557309</v>
       </c>
       <c r="C3">
-        <v>0.1870074637993043</v>
+        <v>0.1807830326054377</v>
       </c>
       <c r="D3">
-        <v>0.2024277254943559</v>
+        <v>0.1961230888607332</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -430,7 +430,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.195 (0.187; 0.202)</t>
+          <t>0.188 (0.181; 0.196)</t>
         </is>
       </c>
     </row>
@@ -439,13 +439,13 @@
         <v>2011</v>
       </c>
       <c r="B4">
-        <v>0.1688509823713639</v>
+        <v>0.1588775516555963</v>
       </c>
       <c r="C4">
-        <v>0.1622667675253314</v>
+        <v>0.1524498799307465</v>
       </c>
       <c r="D4">
-        <v>0.1756463455445354</v>
+        <v>0.1655233036378536</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -454,7 +454,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.169 (0.162; 0.176)</t>
+          <t>0.159 (0.152; 0.166)</t>
         </is>
       </c>
     </row>
@@ -463,13 +463,13 @@
         <v>2012</v>
       </c>
       <c r="B5">
-        <v>0.162006912218313</v>
+        <v>0.1533785119101977</v>
       </c>
       <c r="C5">
-        <v>0.1549565015291381</v>
+        <v>0.1464867572914501</v>
       </c>
       <c r="D5">
-        <v>0.1693138380137139</v>
+        <v>0.1605335184267223</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.162 (0.155; 0.169)</t>
+          <t>0.153 (0.146; 0.161)</t>
         </is>
       </c>
     </row>
@@ -487,13 +487,13 @@
         <v>2013</v>
       </c>
       <c r="B6">
-        <v>0.1361689608549603</v>
+        <v>0.129039546333056</v>
       </c>
       <c r="C6">
-        <v>0.1299472332262041</v>
+        <v>0.1229378898100027</v>
       </c>
       <c r="D6">
-        <v>0.1426397407133448</v>
+        <v>0.1353972895944564</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.136 (0.13; 0.143)</t>
+          <t>0.129 (0.123; 0.135)</t>
         </is>
       </c>
     </row>
@@ -511,13 +511,13 @@
         <v>2014</v>
       </c>
       <c r="B7">
-        <v>0.1386134009142055</v>
+        <v>0.1293297020171072</v>
       </c>
       <c r="C7">
-        <v>0.1313024371924645</v>
+        <v>0.1222297391865807</v>
       </c>
       <c r="D7">
-        <v>0.1462629018700465</v>
+        <v>0.1367778162767496</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.139 (0.131; 0.146)</t>
+          <t>0.129 (0.122; 0.137)</t>
         </is>
       </c>
     </row>
@@ -535,13 +535,13 @@
         <v>2015</v>
       </c>
       <c r="B8">
-        <v>0.1369382510925666</v>
+        <v>0.127928868517252</v>
       </c>
       <c r="C8">
-        <v>0.1298998286714454</v>
+        <v>0.1210619924260343</v>
       </c>
       <c r="D8">
-        <v>0.1442947950012732</v>
+        <v>0.1351253663993232</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.137 (0.13; 0.144)</t>
+          <t>0.128 (0.121; 0.135)</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
         <v>2016</v>
       </c>
       <c r="B9">
-        <v>0.1569720514345517</v>
+        <v>0.1504531299180593</v>
       </c>
       <c r="C9">
-        <v>0.1498807727985143</v>
+        <v>0.1434800366603729</v>
       </c>
       <c r="D9">
-        <v>0.164333982216654</v>
+        <v>0.1577027171001625</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.157 (0.15; 0.164)</t>
+          <t>0.15 (0.143; 0.158)</t>
         </is>
       </c>
     </row>
@@ -583,13 +583,13 @@
         <v>2017</v>
       </c>
       <c r="B10">
-        <v>0.1497257055118416</v>
+        <v>0.141659867779722</v>
       </c>
       <c r="C10">
-        <v>0.1424074094235416</v>
+        <v>0.1345159238062075</v>
       </c>
       <c r="D10">
-        <v>0.1573510834844369</v>
+        <v>0.1491178470061186</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.15 (0.142; 0.157)</t>
+          <t>0.142 (0.135; 0.149)</t>
         </is>
       </c>
     </row>
@@ -607,13 +607,13 @@
         <v>2018</v>
       </c>
       <c r="B11">
-        <v>0.1567931263160164</v>
+        <v>0.1505458984610124</v>
       </c>
       <c r="C11">
-        <v>0.1495448064752867</v>
+        <v>0.1434069031576103</v>
       </c>
       <c r="D11">
-        <v>0.1643248844533061</v>
+        <v>0.1579747412632428</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.157 (0.15; 0.164)</t>
+          <t>0.151 (0.143; 0.158)</t>
         </is>
       </c>
     </row>
@@ -631,13 +631,13 @@
         <v>2019</v>
       </c>
       <c r="B12">
-        <v>0.1536453029926477</v>
+        <v>0.1482012151343012</v>
       </c>
       <c r="C12">
-        <v>0.1464283873991061</v>
+        <v>0.1410597626697253</v>
       </c>
       <c r="D12">
-        <v>0.1611507599947551</v>
+        <v>0.1556387063515071</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.154 (0.146; 0.161)</t>
+          <t>0.148 (0.141; 0.156)</t>
         </is>
       </c>
     </row>
@@ -655,13 +655,13 @@
         <v>2020</v>
       </c>
       <c r="B13">
-        <v>0.1465041374006892</v>
+        <v>0.1413962789450828</v>
       </c>
       <c r="C13">
-        <v>0.1361740945350104</v>
+        <v>0.1312218595559212</v>
       </c>
       <c r="D13">
-        <v>0.1574749530574707</v>
+        <v>0.1522213593815907</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.147 (0.136; 0.157)</t>
+          <t>0.141 (0.131; 0.152)</t>
         </is>
       </c>
     </row>
@@ -679,13 +679,13 @@
         <v>2021</v>
       </c>
       <c r="B14">
-        <v>0.1109489108022232</v>
+        <v>0.1082689025852364</v>
       </c>
       <c r="C14">
-        <v>0.1010778169405662</v>
+        <v>0.0984699535937833</v>
       </c>
       <c r="D14">
-        <v>0.1216535395084216</v>
+        <v>0.1189143450459205</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.111 (0.101; 0.122)</t>
+          <t>0.108 (0.098; 0.119)</t>
         </is>
       </c>
     </row>
@@ -703,13 +703,13 @@
         <v>2023</v>
       </c>
       <c r="B15">
-        <v>0.1326241114629677</v>
+        <v>0.1251115432501728</v>
       </c>
       <c r="C15">
-        <v>0.1223920208494742</v>
+        <v>0.1152414857289895</v>
       </c>
       <c r="D15">
-        <v>0.1435716740507878</v>
+        <v>0.1356972877001454</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.133 (0.122; 0.144)</t>
+          <t>0.125 (0.115; 0.136)</t>
         </is>
       </c>
     </row>
